--- a/5/search/FY5_Missile2_results/top10_solutions.xlsx
+++ b/5/search/FY5_Missile2_results/top10_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>117</v>
       </c>
       <c r="B2" t="n">
-        <v>134.4</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -499,24 +499,94 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>11779.6735367001</v>
+        <v>11783.30546069801</v>
       </c>
       <c r="F2" t="n">
-        <v>395.0255370183327</v>
+        <v>387.8974848248258</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>11779.6735367001</v>
+        <v>11783.30546069801</v>
       </c>
       <c r="I2" t="n">
-        <v>395.0255370183327</v>
+        <v>387.8974848248258</v>
       </c>
       <c r="J2" t="n">
         <v>1300</v>
       </c>
       <c r="K2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>126</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11683.30361691581</v>
+      </c>
+      <c r="F3" t="n">
+        <v>148.6532141723128</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11551.63397860739</v>
+      </c>
+      <c r="I3" t="n">
+        <v>363.5185355895441</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>132</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11620.60378914989</v>
+      </c>
+      <c r="F4" t="n">
+        <v>250.9700338948037</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11551.63397860739</v>
+      </c>
+      <c r="I4" t="n">
+        <v>363.5185355895439</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1295.1</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
     </row>
